--- a/2083_2084/estimate/budget maag estimate/ओपी खोला रातोमाटे खानेपानी/ओपी खोला रातोमाटे खानेपानी.xlsx
+++ b/2083_2084/estimate/budget maag estimate/ओपी खोला रातोमाटे खानेपानी/ओपी खोला रातोमाटे खानेपानी.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F0113D-C5A3-4724-9206-C5F4D84F8EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1783379-5F56-4B46-BEDF-E35A5C285BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,6 +169,24 @@
     <t>-for pipe laying for tap distribution</t>
   </si>
   <si>
+    <t>-for 50mm pipe laying for distribution</t>
+  </si>
+  <si>
+    <t>Laying and joining of 50 mmØ HDPE pipe with butt-weld joints</t>
+  </si>
+  <si>
+    <t>g/d k|sf/sf] Sn] / l;N6L df6f]df ;j} lsl;dsf] vGg] sfd</t>
+  </si>
+  <si>
+    <t>GI pipe threaded light class 50mm</t>
+  </si>
+  <si>
+    <t>F.Y.: 2083/2084</t>
+  </si>
+  <si>
+    <t>Date: 2083/07/13</t>
+  </si>
+  <si>
     <r>
       <t>Project:-</t>
     </r>
@@ -184,26 +202,8 @@
         <sz val="14"/>
         <rFont val="Preeti"/>
       </rPr>
-      <t>cf]kL vf]nf /ftf]df6]</t>
+      <t>cf]kL vf]nf /ftf]df6] l;FrfO</t>
     </r>
-  </si>
-  <si>
-    <t>-for 50mm pipe laying for distribution</t>
-  </si>
-  <si>
-    <t>Laying and joining of 50 mmØ HDPE pipe with butt-weld joints</t>
-  </si>
-  <si>
-    <t>g/d k|sf/sf] Sn] / l;N6L df6f]df ;j} lsl;dsf] vGg] sfd</t>
-  </si>
-  <si>
-    <t>GI pipe threaded light class 50mm</t>
-  </si>
-  <si>
-    <t>F.Y.: 2083/2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:                  </t>
   </si>
 </sst>
 </file>
@@ -485,6 +485,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -506,24 +524,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1079,113 +1079,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
     </row>
     <row r="6" spans="1:25" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="A6" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-    </row>
-    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -1256,8 +1256,8 @@
       <c r="A10" s="17">
         <v>1</v>
       </c>
-      <c r="B10" s="54" t="s">
-        <v>42</v>
+      <c r="B10" s="41" t="s">
+        <v>41</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -1291,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="20">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E11" s="19">
         <v>0.15</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G11" s="20">
         <f t="shared" ref="G11" si="0">PRODUCT(C11:F11)</f>
-        <v>16.875</v>
+        <v>17.55</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
@@ -1319,7 +1319,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="38">
         <f>SUM(G11:G11)</f>
-        <v>16.875</v>
+        <v>17.55</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>28</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J12" s="38">
         <f>G12*I12</f>
-        <v>12166.875</v>
+        <v>12653.550000000001</v>
       </c>
       <c r="K12" s="14"/>
       <c r="M12" s="9"/>
@@ -1364,7 +1364,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -1400,13 +1400,13 @@
       </c>
       <c r="D15" s="20">
         <f>D11</f>
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="20">
         <f t="shared" ref="G15" si="1">PRODUCT(C15:F15)</f>
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -1424,7 +1424,7 @@
       <c r="F16" s="14"/>
       <c r="G16" s="38">
         <f>SUM(G15:G15)</f>
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>35</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="J16" s="38">
         <f>G16*I16</f>
-        <v>1727.5</v>
+        <v>1796.6000000000001</v>
       </c>
       <c r="K16" s="14"/>
       <c r="M16" s="9"/>
@@ -1503,7 +1503,7 @@
     <row r="19" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="22">
         <f>C15</f>
@@ -1511,18 +1511,18 @@
       </c>
       <c r="D19" s="31">
         <f>D15</f>
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E19" s="22">
-        <v>0.80800000000000005</v>
+        <v>0.746</v>
       </c>
       <c r="F19" s="22">
         <f>C19*D19*E19</f>
-        <v>202</v>
+        <v>193.96</v>
       </c>
       <c r="G19" s="31">
         <f>F19</f>
-        <v>202</v>
+        <v>193.96</v>
       </c>
       <c r="H19" s="22"/>
       <c r="I19" s="22"/>
@@ -1553,7 +1553,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="2">
         <f>SUM(G19:G19)</f>
-        <v>202</v>
+        <v>193.96</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>32</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="J20" s="16">
         <f>G20*I20</f>
-        <v>63630</v>
+        <v>61097.4</v>
       </c>
       <c r="K20" s="14"/>
     </row>
@@ -1585,7 +1585,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="13">
         <v>1</v>
@@ -1680,7 +1680,7 @@
       <c r="I26" s="16"/>
       <c r="J26" s="16">
         <f>SUM(J10:J24)</f>
-        <v>86484.375</v>
+        <v>84507.55</v>
       </c>
       <c r="K26" s="29"/>
       <c r="M26" s="10"/>
@@ -1702,11 +1702,11 @@
       <c r="B28" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="49">
+      <c r="C28" s="42">
         <f>J26</f>
-        <v>86484.375</v>
-      </c>
-      <c r="D28" s="50"/>
+        <v>84507.55</v>
+      </c>
+      <c r="D28" s="43"/>
       <c r="E28" s="31">
         <v>100</v>
       </c>
@@ -1734,49 +1734,49 @@
       <c r="B29" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="44">
         <v>75000</v>
       </c>
-      <c r="D29" s="52"/>
+      <c r="D29" s="45"/>
       <c r="E29" s="31"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="44">
         <f>C29-C32-C33</f>
         <v>71250</v>
       </c>
-      <c r="D30" s="52"/>
+      <c r="D30" s="45"/>
       <c r="E30" s="31">
         <f>C30/C28*100</f>
-        <v>82.384823848238483</v>
+        <v>84.311993425439496</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="53">
+      <c r="C31" s="46">
         <f>C28-C30</f>
-        <v>15234.375</v>
-      </c>
-      <c r="D31" s="53"/>
+        <v>13257.550000000003</v>
+      </c>
+      <c r="D31" s="46"/>
       <c r="E31" s="31">
         <f>100-E30</f>
-        <v>17.615176151761517</v>
+        <v>15.688006574560504</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="42">
         <f>C29*0.03</f>
         <v>2250</v>
       </c>
-      <c r="D32" s="50"/>
+      <c r="D32" s="43"/>
       <c r="E32" s="31">
         <v>3</v>
       </c>
@@ -1785,23 +1785,17 @@
       <c r="B33" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="42">
         <f>C29*0.02</f>
         <v>1500</v>
       </c>
-      <c r="D33" s="50"/>
+      <c r="D33" s="43"/>
       <c r="E33" s="31">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -1811,6 +1805,12 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
